--- a/salida/registro_cambios.xlsx
+++ b/salida/registro_cambios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,6 +1100,218 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cra 77 # 71 - 43</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:30:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cra 77 # 71 - 43</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:31:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cra 77 # 71 - 43</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:32:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cra 77 # 71 - 43</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:32:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cra 77 # 71 - 43</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:40:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cra 77 # 71 - 43</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DET6381868421</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://trk.la/avlSrq1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-02-08 12:40:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/salida/registro_cambios.xlsx
+++ b/salida/registro_cambios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2250,6 +2250,166 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>634</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PROCEINCA SAS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DET6386864687</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://trk.la/anjqoCp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-03-09 09:49:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8539</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>INDUSTRIAS DIMALTA LIMITADA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DET6386864689</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://trk.la/anjqomA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-03-09 09:49:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>8538</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DET6386864690</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://trk.la/anjqo42</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-03-09 09:49:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>634</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PROCEINCA SAS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DET6386864904</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://trk.la/anjqgAX</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-03-09 09:50:24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/salida/registro_cambios.xlsx
+++ b/salida/registro_cambios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2410,6 +2410,7510 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DET6387564727</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CP3f</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DET6387564732</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CP43</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DET6387564737</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CP5W</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DET6387564742</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CP0q</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DET6387564748</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CPGl</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DET6387564749</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CPla</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DET6387564752</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CPuz</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DET6387564753</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CPvu</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DET6387564754</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CPn9</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DET6387565132</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CfAG</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DET6387565146</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CfHs</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DET6387565166</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cf4L</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DET6387565186</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cfue</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DET6387565206</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Crom</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DET6387565224</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CrOP</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DET6387565243</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cr7N</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DET6387565266</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CtjU</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DET6387565301</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CtTz</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:18:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DET6387566009</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cxw5</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DET6387566010</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CxjB</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DET6387566011</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CxER</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DET6387566012</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cxog</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DET6387566014</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CxHb</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DET6387566016</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cxg6</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DET6387566017</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CxVP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DET6387566018</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CxNW</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DET6387566020</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CxUL</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:21:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DET6387566391</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CsPy</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DET6387566401</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cs39</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DET6387566403</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CsCC</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>DET6387566405</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CsmX</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>DET6387566407</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CsqY</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DET6387566408</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Csp4</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DET6387566410</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CsDh</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>DET6387566411</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2Cs5E</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DET6387566412</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2CsxM</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:26:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DET6387567115</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLyW</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DET6387567119</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLRZ</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DET6387567123</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WL8o</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DET6387567126</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLjl</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>DET6387567127</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLEa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DET6387567128</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLoI</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DET6387567133</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLVN</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DET6387567137</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLYe</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DET6387567142</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2WLfE</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-03-13 07:35:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>DET6387594206</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25yLy</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>DET6387594298</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25AfO</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DET6387594300</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25Atn</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>DET6387594305</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25Ami</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>DET6387594306</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25A4j</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>DET6387594307</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25Aq1</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>DET6387594308</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25App</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DET6387594310</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25ADA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>DET6387594311</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25A52</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:12:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:12:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>DET6387594742</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://trk.la/an258pR</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DET6387594744</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://trk.la/an258D3</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DET6387594745</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2585b</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>DET6387594747</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://trk.la/an258z6</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>DET6387594749</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://trk.la/an258cW</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>DET6387594750</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2580T</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>DET6387594751</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://trk.la/an258TL</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DET6387594753</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://trk.la/an258KZ</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>DET6387594754</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://trk.la/an258Qq</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:13:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>test001</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Dir Test</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>DET6387595031</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25oIc</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:17:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>test002</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Dir Test2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DET6387595040</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25oMp</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:18:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>DET6387595709</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251Ej</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>DET6387595710</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251o1</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DET6387595711</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2512p</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>DET6387595712</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251H7</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>DET6387595725</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251rW</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>DET6387595726</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251tT</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>DET6387595728</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251Ow</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>DET6387595730</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251Wq</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>DET6387595731</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://trk.la/an251mQ</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:27:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DET6387596732</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://trk.la/an255bJ</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DET6387596734</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2550r</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>DET6387596735</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://trk.la/an255Tx</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>DET6387596736</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://trk.la/an255sk</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>DET6387596739</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2557O</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>DET6387596741</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://trk.la/an255ln</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>DET6387596744</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://trk.la/an255um</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>DET6387596746</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://trk.la/an255ni</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DET6387596747</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://trk.la/an255Xj</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:40:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>DET6387597084</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TZ9</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>DET6387597086</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TMC</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>DET6387597087</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TF0</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>DET6387597088</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TfX</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>DET6387597090</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TtY</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>DET6387597092</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TOK</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>DET6387597093</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TCh</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>DET6387597095</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TmM</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>DET6387597097</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25TqG</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:44:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>DET6387597141</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25sVI</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>DET6387597143</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25sPz</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>DET6387597147</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25s1C</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>DET6387597148</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25sM0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>DET6387597152</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25st4</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>DET6387597153</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25s3K</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>DET6387597156</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25sWM</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>DET6387597157</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25smS</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>DET6387597160</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25spH</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:45:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>DET6387597431</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25li6</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>DET6387597432</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25lhP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>DET6387597433</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25lyW</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>DET6387597434</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25lAT</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>DET6387597435</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25lJL</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>DET6387597436</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25law</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>DET6387597437</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25lRZ</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>DET6387597438</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25ldq</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>DET6387597439</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25l9Q</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Cra 77 # 71 - 43</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>DET6387597712</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://trk.la/an25vOk</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:55:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>DET6387597876</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLe9</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>DET6387597877</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLwN</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>DET6387597878</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLjC</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>DET6387597879</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLE0</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>DET6387597880</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLoX</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>DET6387597882</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLHY</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>DET6387597884</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLgK</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>DET6387597885</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLVh</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>DET6387597890</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xLZJ</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:58:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>DET6387599012</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xHtR</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>DET6387599015</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xHCb</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>DET6387599018</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xH4P</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>DET6387599019</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xHqW</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>DET6387599020</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xHpT</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>DET6387599022</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xHDw</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>DET6387599028</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xH0F</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>DET6387599038</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xHuC</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>DET6387599049</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2xIRJ</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:10:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>COLORHOME SAS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>DET6387609807</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2caq5</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>BINGEM SAS</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>DET6387609808</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2capB</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>AT&amp;T SOLUCIONES METALMECANICAS SAS</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>DET6387609810</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2caDg</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>DET6387609811</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2ca53</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>CARIN LUVOV PARDO DIAZ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>DET6387609812</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2caxb</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>8561</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>MAQUINADOS Y MONTAJES S.</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>DET6387609814</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cab6</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>INDUSTRIAS RANDAL SAS</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>DET6387609815</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cacP</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>8560</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>AMANDA REINA QUIÑONEZ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>DET6387609817</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2caTT</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>8559</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>PRODUCTOS Y PARTES SAS</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>DET6387609818</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2casL</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>638</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ANGEL RAUL RINCON ROJAS</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>DET6387609820</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2caQZ</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:20:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>MOLSOPLAST SAS</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>DET6387611268</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cfeA</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:46:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.A.S.</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>DET6387611269</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cfw2</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PLASTISOL IMPERMEABILIZANTES Y POLIMEROS SAS</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>DET6387611270</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cfjf</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>GMB ARQUINOX SAS</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>DET6387611271</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cfE5</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>DET6387611281</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cfYT</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>FUMIREPUESTOS J.A. SAS</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>DET6387611285</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cfFq</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Consumidor Final</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>DET6387611286</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cffQ</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS B &amp; R S.A.S.</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>DET6387611287</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cfry</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CONSORCIO METALURGICO NACIONAL S.A.S.</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>DET6387611289</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2cf3F</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2026-03-13 15:47:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CL 35 SUR 70B 93, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>DET6387613930</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://trk.la/an208dM</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:16:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>8558</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>TV 60 No. 45 A - 85 SUR, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>DET6387613931</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2089S</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:16:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>CL 38 SUR 72 H 21, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>DET6387613932</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2086G</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>CL 2 73 B 39, Bogotá, 11001</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>DET6387613933</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2088J</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CL 39 SUR 68 M 36, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>DET6387613934</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://trk.la/an208eH</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:17:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:17:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>8557</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CR 92 No 66A - 27, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>DET6387613935</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://trk.la/an208wr</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:17:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>8556</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>TV 60 No. 45 A - 85 SUR, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>DET6387613948</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://trk.la/an208Zj</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:17:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>1389</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CL 2 73 B 39, Bogotá, 11001</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>DET6387614295</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202iE</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CR 70 22 90 SUR, Bogotá, 110831</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>DET6387614299</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202JJ</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CL 56A 74 08, Bogotá, 111021</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>DET6387614300</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202aH</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TV 65 A 1 A 33, Bogotá, 111611</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>DET6387614301</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202Rr</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CL 42 A SUR 99 F 22, Bogotá, 110881</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>DET6387614303</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2029k</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>8561</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CR 16 No 60 - 14 BRR LA ESMERALDA, Girón, 00000</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>DET6387614305</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://trk.la/an2028V</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>CL 35 SUR No. 70 B 12, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>DET6387614306</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202eO</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>8560</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>CR 13 No. 23 - 76  BRR GIRARDOT, Bucaramanga, 00000</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>DET6387614307</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202wc</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>8559</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CR 26 A No 26 - 79 SUR, Bogotá, 111511</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>DET6387614308</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202jn</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>638</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CR 27 8 17 P1 BRR RICAURTE, Bogotá, 111411</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>DET6387614309</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://trk.la/an202E8</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>1389</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CL 2 73 B 39, Bogotá, 11001</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>DET6387614482</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20ghJ</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CR 70 22 90 SUR, Bogotá, 110831</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>DET6387614483</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20gyH</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CL 56A 74 08, Bogotá, 111021</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>DET6387614486</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20gak</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TV 65 A 1 A 33, Bogotá, 111611</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>DET6387614487</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20gRd</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CL 42 A SUR 99 F 22, Bogotá, 110881</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>DET6387614488</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20gdV</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>8561</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CR 16 No 60 - 14 BRR LA ESMERALDA, Girón, 00000</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>DET6387614491</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20g8n</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>CL 35 SUR No. 70 B 12, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>DET6387614492</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20ge8</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>8560</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>CR 13 No. 23 - 76  BRR GIRARDOT, Bucaramanga, 00000</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>DET6387614495</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20gEs</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>8559</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>CR 26 A No 26 - 79 SUR, Bogotá, 111511</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>DET6387614496</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20goi</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>638</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>CR 27 8 17 P1 BRR RICAURTE, Bogotá, 111411</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>DET6387614500</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20gg7</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>test001</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Cra 1 # 2 -3</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>DET6387614551</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://trk.la/an20V9c</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>2026-03-13 16:32:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
